--- a/web/files/九龙-西南九龙-汇玺III.xlsx
+++ b/web/files/九龙-西南九龙-汇玺III.xlsx
@@ -120,7 +120,8 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
@@ -136,13 +137,12 @@
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00004D00"/>
+      <color rgb="00000000"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
+      <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -275,7 +275,7 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -284,10 +284,10 @@
     <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1285,12 +1285,12 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1300,12 +1300,12 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -53053,7 +53053,7 @@
       </c>
       <c r="F846" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G846" s="3" t="inlineStr">
@@ -53063,12 +53063,12 @@
       </c>
       <c r="H846" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I846" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J846" s="3" t="inlineStr">
@@ -53078,12 +53078,12 @@
       </c>
       <c r="K846" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L846" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M846" s="3" t="inlineStr">
@@ -53093,7 +53093,7 @@
       </c>
       <c r="N846" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -72537,7 +72537,7 @@
       </c>
       <c r="F1160" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1160" s="3" t="inlineStr">
@@ -72547,12 +72547,12 @@
       </c>
       <c r="H1160" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I1160" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J1160" s="3" t="inlineStr">
@@ -72562,12 +72562,12 @@
       </c>
       <c r="K1160" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L1160" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M1160" s="3" t="inlineStr">
@@ -72577,7 +72577,7 @@
       </c>
       <c r="N1160" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -72607,7 +72607,7 @@
       </c>
       <c r="F1161" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1161" s="3" t="inlineStr">
@@ -72617,12 +72617,12 @@
       </c>
       <c r="H1161" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I1161" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J1161" s="3" t="inlineStr">
@@ -72632,12 +72632,12 @@
       </c>
       <c r="K1161" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L1161" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M1161" s="3" t="inlineStr">
@@ -72647,7 +72647,7 @@
       </c>
       <c r="N1161" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -72879,7 +72879,7 @@
       </c>
       <c r="F1165" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1165" s="3" t="inlineStr">
@@ -72889,12 +72889,12 @@
       </c>
       <c r="H1165" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I1165" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J1165" s="3" t="inlineStr">
@@ -72904,12 +72904,12 @@
       </c>
       <c r="K1165" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L1165" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M1165" s="3" t="inlineStr">
@@ -72919,7 +72919,7 @@
       </c>
       <c r="N1165" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -73399,7 +73399,7 @@
       </c>
       <c r="F1173" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1173" s="3" t="inlineStr">
@@ -73409,12 +73409,12 @@
       </c>
       <c r="H1173" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I1173" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J1173" s="3" t="inlineStr">
@@ -73424,12 +73424,12 @@
       </c>
       <c r="K1173" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L1173" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M1173" s="3" t="inlineStr">
@@ -73439,7 +73439,7 @@
       </c>
       <c r="N1173" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -73582,7 +73582,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -73602,7 +73602,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -73667,9 +73667,9 @@
       <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 1214呎 (4+房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
@@ -73759,7 +73759,7 @@
 (20年-12月-23日)</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 279呎 (开放式)
 $1085万
@@ -74075,7 +74075,7 @@
 (21年-03月-26日)</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 279呎 (开放式)
 $1064万
@@ -74233,7 +74233,7 @@
 (21年-03月-12日)</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 279呎 (开放式)
 $1060万
@@ -74470,7 +74470,7 @@
 (20年-12月-24日)</t>
         </is>
       </c>
-      <c r="D15" s="23" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 279呎 (开放式)
 $1046万
@@ -74628,7 +74628,7 @@
 (21年-03月-31日)</t>
         </is>
       </c>
-      <c r="D17" s="23" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 279呎 (开放式)
 $1039万
@@ -74786,7 +74786,7 @@
 (21年-04月-12日)</t>
         </is>
       </c>
-      <c r="D19" s="23" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 279呎 (开放式)
 $1033万
@@ -75181,7 +75181,7 @@
 (20年-12月-23日)</t>
         </is>
       </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 279呎 (开放式)
 $1018万
@@ -75260,7 +75260,7 @@
 (20年-12月-22日)</t>
         </is>
       </c>
-      <c r="D25" s="23" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>C | 279呎 (开放式)
 $1015万
@@ -75497,7 +75497,7 @@
 (21年-01月-08日)</t>
         </is>
       </c>
-      <c r="D28" s="23" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>C | 279呎 (开放式)
 $1002万
@@ -77353,7 +77353,7 @@
 (19年-10月-23日)</t>
         </is>
       </c>
-      <c r="H5" s="24" t="inlineStr">
+      <c r="H5" s="23" t="inlineStr">
         <is>
           <t>G | 350呎 (1房)
 $1066万
@@ -77456,7 +77456,7 @@
 (19年-10月-16日)</t>
         </is>
       </c>
-      <c r="I6" s="24" t="inlineStr">
+      <c r="I6" s="23" t="inlineStr">
         <is>
           <t>H | 350呎 (1房)
 $1062万
@@ -77464,7 +77464,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="J6" s="24" t="inlineStr">
+      <c r="J6" s="23" t="inlineStr">
         <is>
           <t>J | 354呎 (1房)
 $1069万
@@ -77472,7 +77472,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="K6" s="24" t="inlineStr">
+      <c r="K6" s="23" t="inlineStr">
         <is>
           <t>K | 380呎 (1房)
 $1108万
@@ -80029,7 +80029,7 @@
 (19年-10月-21日)</t>
         </is>
       </c>
-      <c r="J33" s="24" t="inlineStr">
+      <c r="J33" s="23" t="inlineStr">
         <is>
           <t>J | 354呎 (1房)
 $968万
@@ -80987,7 +80987,7 @@
 (19年-10月-17日)</t>
         </is>
       </c>
-      <c r="K43" s="24" t="inlineStr">
+      <c r="K43" s="23" t="inlineStr">
         <is>
           <t>K | 380呎 (1房)
 $991万
@@ -81175,7 +81175,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -81195,7 +81195,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -81255,9 +81255,9 @@
       <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 1513呎 (4+房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
@@ -81702,7 +81702,7 @@
 (21年-03月-14日)</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 275呎 (开放式)
 $928万
@@ -84061,7 +84061,7 @@
 (19年-11月-13日)</t>
         </is>
       </c>
-      <c r="G44" s="23" t="inlineStr">
+      <c r="G44" s="20" t="inlineStr">
         <is>
           <t>F | 350呎 (1房)
 $1172万
@@ -84156,27 +84156,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -84204,6 +84204,52 @@
         </is>
       </c>
       <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 1629呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>B | 1739呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 1573呎 (3房)
+$4806万
+$30,550/呎
+(22年-07月-26日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 1739呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>A | 1629呎 (3房)
 -
@@ -84211,7 +84257,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t>B | 1739呎 (3房)
 -
@@ -84220,52 +84266,6 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>A | 1573呎 (3房)
-$4806万
-$30,550/呎
-(22年-07月-26日)</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 1739呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 1629呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 1739呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
@@ -84283,9 +84283,9 @@
       <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 1739呎 (3房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -84359,27 +84359,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -84452,7 +84452,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>A | 2171呎 (4+房)
 -
@@ -84460,7 +84460,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t>B | 1640呎 (3房)
 -
@@ -84486,9 +84486,9 @@
       <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 1640呎 (3房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
     </row>

--- a/web/files/九龙-西南九龙-汇玺III.xlsx
+++ b/web/files/九龙-西南九龙-汇玺III.xlsx
@@ -25603,14 +25603,14 @@
       </c>
       <c r="J403" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K403" s="5" t="n">
-        <v>7997250</v>
+        <v>8530400</v>
       </c>
       <c r="L403" s="5" t="n">
-        <v>22849</v>
+        <v>24373</v>
       </c>
       <c r="M403" s="3" t="inlineStr">
         <is>
@@ -26099,14 +26099,14 @@
       </c>
       <c r="J411" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K411" s="5" t="n">
-        <v>8309250</v>
+        <v>8863200</v>
       </c>
       <c r="L411" s="5" t="n">
-        <v>21866</v>
+        <v>23324</v>
       </c>
       <c r="M411" s="3" t="inlineStr">
         <is>
@@ -26161,14 +26161,14 @@
       </c>
       <c r="J412" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K412" s="5" t="n">
-        <v>8016750</v>
+        <v>8551200</v>
       </c>
       <c r="L412" s="5" t="n">
-        <v>22646</v>
+        <v>24156</v>
       </c>
       <c r="M412" s="3" t="inlineStr">
         <is>
@@ -26223,14 +26223,14 @@
       </c>
       <c r="J413" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K413" s="5" t="n">
-        <v>7963500</v>
+        <v>8494400</v>
       </c>
       <c r="L413" s="5" t="n">
-        <v>22753</v>
+        <v>24270</v>
       </c>
       <c r="M413" s="3" t="inlineStr">
         <is>
@@ -55867,14 +55867,14 @@
       </c>
       <c r="J891" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K891" s="5" t="n">
-        <v>6960000</v>
+        <v>7424000</v>
       </c>
       <c r="L891" s="5" t="n">
-        <v>25309</v>
+        <v>26996</v>
       </c>
       <c r="M891" s="3" t="inlineStr">
         <is>
@@ -77356,8 +77356,8 @@
       <c r="H5" s="23" t="inlineStr">
         <is>
           <t>G | 350呎 (1房)
-$1066万
-$30,466/呎
+$853.04万
+$24,373/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -77459,24 +77459,24 @@
       <c r="I6" s="23" t="inlineStr">
         <is>
           <t>H | 350呎 (1房)
-$1062万
-$30,337/呎
+$849.44万
+$24,270/呎
 (暂停销售)</t>
         </is>
       </c>
       <c r="J6" s="23" t="inlineStr">
         <is>
           <t>J | 354呎 (1房)
-$1069万
-$30,195/呎
+$855.12万
+$24,156/呎
 (暂停销售)</t>
         </is>
       </c>
       <c r="K6" s="23" t="inlineStr">
         <is>
           <t>K | 380呎 (1房)
-$1108万
-$29,155/呎
+$886.32万
+$23,324/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -81705,8 +81705,8 @@
       <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 275呎 (开放式)
-$928万
-$33,745/呎
+$742.40万
+$26,996/呎
 (在售)</t>
         </is>
       </c>

--- a/web/files/九龙-西南九龙-汇玺III.xlsx
+++ b/web/files/九龙-西南九龙-汇玺III.xlsx
@@ -25603,14 +25603,14 @@
       </c>
       <c r="J403" s="3" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K403" s="5" t="n">
-        <v>8530400</v>
+        <v>7997250</v>
       </c>
       <c r="L403" s="5" t="n">
-        <v>24373</v>
+        <v>22849</v>
       </c>
       <c r="M403" s="3" t="inlineStr">
         <is>
@@ -26099,14 +26099,14 @@
       </c>
       <c r="J411" s="3" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K411" s="5" t="n">
-        <v>8863200</v>
+        <v>8309250</v>
       </c>
       <c r="L411" s="5" t="n">
-        <v>23324</v>
+        <v>21866</v>
       </c>
       <c r="M411" s="3" t="inlineStr">
         <is>
@@ -26161,14 +26161,14 @@
       </c>
       <c r="J412" s="3" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K412" s="5" t="n">
-        <v>8551200</v>
+        <v>8016750</v>
       </c>
       <c r="L412" s="5" t="n">
-        <v>24156</v>
+        <v>22646</v>
       </c>
       <c r="M412" s="3" t="inlineStr">
         <is>
@@ -26223,14 +26223,14 @@
       </c>
       <c r="J413" s="3" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K413" s="5" t="n">
-        <v>8494400</v>
+        <v>7963500</v>
       </c>
       <c r="L413" s="5" t="n">
-        <v>24270</v>
+        <v>22753</v>
       </c>
       <c r="M413" s="3" t="inlineStr">
         <is>
@@ -55867,14 +55867,14 @@
       </c>
       <c r="J891" s="3" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K891" s="5" t="n">
-        <v>7424000</v>
+        <v>6960000</v>
       </c>
       <c r="L891" s="5" t="n">
-        <v>26996</v>
+        <v>25309</v>
       </c>
       <c r="M891" s="3" t="inlineStr">
         <is>
@@ -77356,8 +77356,8 @@
       <c r="H5" s="23" t="inlineStr">
         <is>
           <t>G | 350呎 (1房)
-$853.04万
-$24,373/呎
+$1066万
+$30,466/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -77459,24 +77459,24 @@
       <c r="I6" s="23" t="inlineStr">
         <is>
           <t>H | 350呎 (1房)
-$849.44万
-$24,270/呎
+$1062万
+$30,337/呎
 (暂停销售)</t>
         </is>
       </c>
       <c r="J6" s="23" t="inlineStr">
         <is>
           <t>J | 354呎 (1房)
-$855.12万
-$24,156/呎
+$1069万
+$30,195/呎
 (暂停销售)</t>
         </is>
       </c>
       <c r="K6" s="23" t="inlineStr">
         <is>
           <t>K | 380呎 (1房)
-$886.32万
-$23,324/呎
+$1108万
+$29,155/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -81705,8 +81705,8 @@
       <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 275呎 (开放式)
-$742.40万
-$26,996/呎
+$928万
+$33,745/呎
 (在售)</t>
         </is>
       </c>
